--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -156,7 +156,7 @@
     <t>typeEnseignementSpecialise</t>
   </si>
   <si>
-    <t>Type d'enseignement spécialisé</t>
+    <t>Type enseignement spécialisé</t>
   </si>
   <si>
     <t>diplome</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -139,18 +139,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>niveauScolaireReel</t>
-  </si>
-  <si>
-    <t>Niveau scolaire réel</t>
-  </si>
-  <si>
-    <t>niveauScolaireSuivi</t>
-  </si>
-  <si>
-    <t>Niveau scolaire suivi</t>
   </si>
   <si>
     <t>typeEnseignementSpecialise</t>
@@ -478,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -531,30 +519,6 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CodeSystem for the Observation school period</t>
+    <t>CodeSystem pour l'Observation de la Période Scolaire.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
